--- a/publication_tables/main/table3.xlsx
+++ b/publication_tables/main/table3.xlsx
@@ -608,90 +608,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Table 3. Leakage brackets for the first reversal against universal cash</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Exclusion (%)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Note. Cells are means across ten stratified recipient draws. Leakage is evaluated in two-percentage-point increments. A dash indicates no reversal within the feasible evaluated grid. Source: model simulations.</t>
+          <t>Share of eligible persons excluded, percent. Values follow the displayed precision of Table 3. Leakage brackets for the first reversal against universal cash. Full-precision simulation results accompany the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Last leakage with targeting advantage (%)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Last evaluated leakage rate at which targeted cash has a lower mean FGT1, percent. Values follow the displayed precision of Table 3. Leakage brackets for the first reversal against universal cash. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>First leakage with universal advantage (%)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>First evaluated leakage rate at which universal cash has a lower mean FGT1, percent. Values follow the displayed precision of Table 3. Leakage brackets for the first reversal against universal cash. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Exclusion (%)</t>
+          <t>Maximum feasible grid leakage (%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Share of the eligible target population excluded from receipt (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Last leakage with targeting advantage (%)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Last evaluated leakage rate with lower mean FGT1 under targeting (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>First leakage with universal advantage (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>First evaluated leakage rate with lower mean FGT1 under universal cash (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Maximum feasible grid leakage (%)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Maximum feasible leakage rate on the evaluated grid (%).</t>
+          <t>Maximum feasible leakage on the evaluated grid, percent. Values follow the displayed precision of Table 3. Leakage brackets for the first reversal against universal cash. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
